--- a/tame_output/ON/bt/strategyON_20231015.xlsx
+++ b/tame_output/ON/bt/strategyON_20231015.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.1%</t>
+          <t>130.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1750"/>
+  <dimension ref="A1:G1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41760,7 +41760,7 @@
         <v>45212</v>
       </c>
       <c r="B1750" t="n">
-        <v>2.806683821769451</v>
+        <v>2.806485551981399</v>
       </c>
       <c r="C1750" t="n">
         <v>2.950500122107244</v>
@@ -41776,6 +41776,29 @@
       </c>
       <c r="G1750" t="n">
         <v>4.247968569725085</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="2" t="n">
+        <v>45213</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>2.805336308940817</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>2.950191610492619</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>1.562033387936488</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>3.574648541353468</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>2.161576918479115</v>
+      </c>
+      <c r="G1751" t="n">
+        <v>4.24713776158009</v>
       </c>
     </row>
   </sheetData>
